--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/jun-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>69740545</v>
+        <v>77199.2</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>319999.33</v>
+        <v>354.22</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1499999.4</v>
+        <v>1660.42</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8561399.720000001</v>
+        <v>9477.030000000001</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10769954.7</v>
+        <v>11921.79</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>22000000.29</v>
+        <v>24352.87</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>570000.36</v>
+        <v>630.96</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>44000</v>
+        <v>48.71</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>33129909.58</v>
+        <v>36673.11</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9746999.16</v>
+        <v>10789.43</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>14060480.7</v>
+        <v>15564.23</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>88000</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5579285.43</v>
+        <v>6175.98</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1143882.96</v>
+        <v>1266.22</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6349800.31</v>
+        <v>7028.9</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6098400</v>
+        <v>6750.62</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>42000000.24</v>
+        <v>46491.84</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>23836829.91</v>
+        <v>26386.15</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2507999.55</v>
+        <v>2776.23</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>382800</v>
+        <v>423.74</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>3547300.99</v>
+        <v>3926.68</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>32773115.87</v>
+        <v>36278.16</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>70000007.19</v>
+        <v>77486.41</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>22321200.21</v>
+        <v>24708.42</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>138526434.75</v>
+        <v>153341.65</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>19134520.81</v>
+        <v>21180.93</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>13160159.54</v>
+        <v>14567.62</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>52503588.79</v>
+        <v>58118.77</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>565250</v>
+        <v>625.7</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7959384.73</v>
+        <v>8810.629999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11400000.44</v>
+        <v>12619.21</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>801039.52</v>
+        <v>886.71</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1100000.24</v>
+        <v>1217.64</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1661919.79</v>
+        <v>1839.66</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1753699.43</v>
+        <v>1941.26</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12000000.88</v>
+        <v>13283.38</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5242642.24</v>
+        <v>5803.34</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7557250.06</v>
+        <v>8365.49</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2239900.35</v>
+        <v>2479.45</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>9747000.289999999</v>
+        <v>10789.43</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11999999.75</v>
+        <v>13283.38</v>
       </c>
     </row>
     <row r="43">
@@ -3066,11 +3066,11 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>13308929.95</v>
+        <v>14732.3</v>
       </c>
     </row>
     <row r="44">
@@ -3127,11 +3127,11 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6890400</v>
+        <v>7627.32</v>
       </c>
     </row>
     <row r="45">
@@ -3188,11 +3188,11 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>799999.46</v>
+        <v>885.5599999999999</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>13566000</v>
+        <v>15016.86</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1474000</v>
+        <v>1631.64</v>
       </c>
     </row>
     <row r="48">
@@ -3371,11 +3371,11 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>71249999.91</v>
+        <v>78870.09</v>
       </c>
     </row>
     <row r="49">
@@ -3432,11 +3432,11 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>617499.45</v>
+        <v>683.54</v>
       </c>
     </row>
     <row r="50">
@@ -3493,11 +3493,11 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>695399.9399999999</v>
+        <v>769.77</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>12000935.8</v>
+        <v>13284.42</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>304950.11</v>
+        <v>337.56</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2386711.6</v>
+        <v>2641.97</v>
       </c>
     </row>
     <row r="54">
@@ -3737,11 +3737,11 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>450299.63</v>
+        <v>498.46</v>
       </c>
     </row>
     <row r="55">
@@ -3798,11 +3798,11 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1242188.64</v>
+        <v>1375.04</v>
       </c>
     </row>
     <row r="56">
@@ -3859,11 +3859,11 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>7000000.61</v>
+        <v>7748.64</v>
       </c>
     </row>
     <row r="57">
@@ -3920,11 +3920,11 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>521550.52</v>
+        <v>577.33</v>
       </c>
     </row>
     <row r="58">
@@ -3981,11 +3981,11 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>29700000.84</v>
+        <v>32876.37</v>
       </c>
     </row>
     <row r="59">
@@ -4042,11 +4042,11 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>17099999.53</v>
+        <v>18928.82</v>
       </c>
     </row>
     <row r="60">
@@ -4103,11 +4103,11 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1056399.12</v>
+        <v>1169.38</v>
       </c>
     </row>
     <row r="61">
@@ -4164,11 +4164,11 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4654050.31</v>
+        <v>5151.79</v>
       </c>
     </row>
     <row r="62">
@@ -4225,11 +4225,11 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>886350.4399999999</v>
+        <v>981.14</v>
       </c>
     </row>
     <row r="63">
@@ -4286,11 +4286,11 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>23349860.25</v>
+        <v>25847.1</v>
       </c>
     </row>
     <row r="64">
@@ -4347,11 +4347,11 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>11305000</v>
+        <v>12514.05</v>
       </c>
     </row>
     <row r="65">
@@ -4408,11 +4408,11 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>42293525.52</v>
+        <v>46816.76</v>
       </c>
     </row>
     <row r="66">
@@ -4469,11 +4469,11 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8179499.87</v>
+        <v>9054.290000000001</v>
       </c>
     </row>
     <row r="67">
@@ -4530,11 +4530,11 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1500000.53</v>
+        <v>1660.42</v>
       </c>
     </row>
     <row r="68">
@@ -4591,11 +4591,11 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1897149.71</v>
+        <v>2100.05</v>
       </c>
     </row>
     <row r="69">
@@ -4652,11 +4652,11 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>22610000</v>
+        <v>25028.11</v>
       </c>
     </row>
     <row r="70">
@@ -4713,11 +4713,11 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>32621548.6</v>
+        <v>36110.38</v>
       </c>
     </row>
     <row r="71">
@@ -4774,11 +4774,11 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3712600.44</v>
+        <v>4109.66</v>
       </c>
     </row>
     <row r="72">
@@ -4835,11 +4835,11 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>361200.4</v>
+        <v>399.83</v>
       </c>
     </row>
     <row r="73">
@@ -4896,11 +4896,11 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4976100.37</v>
+        <v>5508.29</v>
       </c>
     </row>
     <row r="74">
@@ -4957,11 +4957,11 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>13796850.36</v>
+        <v>15272.4</v>
       </c>
     </row>
     <row r="75">
@@ -5018,11 +5018,11 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>55865700.31</v>
+        <v>61840.46</v>
       </c>
     </row>
     <row r="76">
@@ -5079,11 +5079,11 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>712087.2</v>
+        <v>788.24</v>
       </c>
     </row>
     <row r="77">
@@ -5140,11 +5140,11 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>19950000.2</v>
+        <v>22083.63</v>
       </c>
     </row>
     <row r="78">
@@ -5201,11 +5201,11 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>46163040</v>
+        <v>51100.11</v>
       </c>
     </row>
     <row r="79">
@@ -5262,11 +5262,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>546249.6899999999</v>
+        <v>604.67</v>
       </c>
     </row>
     <row r="80">
@@ -5323,11 +5323,11 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>882839.76</v>
+        <v>977.26</v>
       </c>
     </row>
     <row r="81">
@@ -5384,11 +5384,11 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>24303600</v>
+        <v>26902.84</v>
       </c>
     </row>
     <row r="82">
@@ -5445,11 +5445,11 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4522000</v>
+        <v>5005.62</v>
       </c>
     </row>
     <row r="83">
@@ -5506,11 +5506,11 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>66499999.53</v>
+        <v>73612.08</v>
       </c>
     </row>
     <row r="84">
@@ -5567,11 +5567,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2039987.25</v>
+        <v>2258.16</v>
       </c>
     </row>
     <row r="85">
@@ -5628,11 +5628,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>26285740.48</v>
+        <v>29096.96</v>
       </c>
     </row>
     <row r="86">
@@ -5689,11 +5689,11 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>38690270.44</v>
+        <v>42828.14</v>
       </c>
     </row>
     <row r="87">
@@ -5750,11 +5750,11 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1099998.24</v>
+        <v>1217.64</v>
       </c>
     </row>
     <row r="88">
@@ -5811,11 +5811,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2535676</v>
+        <v>2806.86</v>
       </c>
     </row>
     <row r="89">
@@ -5872,11 +5872,11 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15304499.86</v>
+        <v>16941.29</v>
       </c>
     </row>
     <row r="90">
@@ -5933,11 +5933,11 @@
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>448800</v>
+        <v>496.8</v>
       </c>
     </row>
     <row r="91">
@@ -5994,11 +5994,11 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>10571124.62</v>
+        <v>11701.69</v>
       </c>
     </row>
     <row r="92">
@@ -6055,11 +6055,11 @@
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2999995.41</v>
+        <v>3320.84</v>
       </c>
     </row>
     <row r="93">
@@ -6116,11 +6116,11 @@
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>960000.25</v>
+        <v>1062.67</v>
       </c>
     </row>
     <row r="94">
@@ -6177,11 +6177,11 @@
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>880650.46</v>
+        <v>974.83</v>
       </c>
     </row>
     <row r="95">
@@ -6238,11 +6238,11 @@
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>19878750.44</v>
+        <v>22004.76</v>
       </c>
     </row>
     <row r="96">
@@ -6299,11 +6299,11 @@
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>760001.24</v>
+        <v>841.28</v>
       </c>
     </row>
     <row r="97">
@@ -6360,11 +6360,11 @@
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3000000.08</v>
+        <v>3320.85</v>
       </c>
     </row>
     <row r="98">
@@ -6421,11 +6421,11 @@
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>69800000.26000001</v>
+        <v>77265.00999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6482,11 +6482,11 @@
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>5878600</v>
+        <v>6507.31</v>
       </c>
     </row>
     <row r="100">
@@ -6547,11 +6547,11 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>191457341.18</v>
+        <v>211933.44</v>
       </c>
     </row>
     <row r="101">
@@ -6608,11 +6608,11 @@
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5275825.31</v>
+        <v>5840.07</v>
       </c>
     </row>
     <row r="102">
@@ -6669,11 +6669,11 @@
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>5999999.87</v>
+        <v>6641.69</v>
       </c>
     </row>
     <row r="103">
@@ -6730,11 +6730,11 @@
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>13000750</v>
+        <v>14391.16</v>
       </c>
     </row>
     <row r="104">
@@ -6791,11 +6791,11 @@
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>8510099.9</v>
+        <v>9420.24</v>
       </c>
     </row>
     <row r="105">
@@ -6852,11 +6852,11 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>13632500.53</v>
+        <v>15090.48</v>
       </c>
     </row>
     <row r="106">
@@ -6913,11 +6913,11 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>159599.47</v>
+        <v>176.67</v>
       </c>
     </row>
     <row r="107">
@@ -6974,11 +6974,11 @@
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>13257249.15</v>
+        <v>14675.09</v>
       </c>
     </row>
     <row r="108">
@@ -7035,11 +7035,11 @@
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>188100.5</v>
+        <v>208.22</v>
       </c>
     </row>
     <row r="109">
@@ -7096,11 +7096,11 @@
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4578240.11</v>
+        <v>5067.88</v>
       </c>
     </row>
     <row r="110">
@@ -7157,11 +7157,11 @@
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>12403200.48</v>
+        <v>13729.71</v>
       </c>
     </row>
     <row r="111">
@@ -7218,11 +7218,11 @@
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12443342.28</v>
+        <v>13774.14</v>
       </c>
     </row>
     <row r="112">
@@ -7279,11 +7279,11 @@
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>205199.32</v>
+        <v>227.15</v>
       </c>
     </row>
     <row r="113">
@@ -7340,11 +7340,11 @@
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>12714301.65</v>
+        <v>14074.08</v>
       </c>
     </row>
     <row r="114">
@@ -7401,11 +7401,11 @@
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6179940.43</v>
+        <v>6840.88</v>
       </c>
     </row>
     <row r="115">
@@ -7462,11 +7462,11 @@
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7016700.35</v>
+        <v>7767.13</v>
       </c>
     </row>
     <row r="116">
@@ -7523,11 +7523,11 @@
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4483902.15</v>
+        <v>4963.45</v>
       </c>
     </row>
     <row r="117">
@@ -7584,11 +7584,11 @@
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6313833.68</v>
+        <v>6989.09</v>
       </c>
     </row>
     <row r="118">
@@ -7645,11 +7645,11 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>16957500</v>
+        <v>18771.08</v>
       </c>
     </row>
     <row r="119">
@@ -7706,11 +7706,11 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>25288049.36</v>
+        <v>27992.57</v>
       </c>
     </row>
     <row r="120">
@@ -7767,11 +7767,11 @@
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3318656</v>
+        <v>3673.58</v>
       </c>
     </row>
     <row r="121">
@@ -7828,11 +7828,11 @@
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>6406800.12</v>
+        <v>7092</v>
       </c>
     </row>
     <row r="122">
@@ -7889,11 +7889,11 @@
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>70000000.40000001</v>
+        <v>77486.39999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7950,11 +7950,11 @@
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>817949.53</v>
+        <v>905.4299999999999</v>
       </c>
     </row>
     <row r="124">
@@ -8011,11 +8011,11 @@
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>90000.24000000001</v>
+        <v>99.63</v>
       </c>
     </row>
     <row r="125">
@@ -8072,11 +8072,11 @@
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>11519200</v>
+        <v>12751.16</v>
       </c>
     </row>
     <row r="126">
@@ -8133,11 +8133,11 @@
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>8987680.75</v>
+        <v>9948.9</v>
       </c>
     </row>
     <row r="127">
@@ -8194,11 +8194,11 @@
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>10972500.73</v>
+        <v>12145.99</v>
       </c>
     </row>
     <row r="128">
@@ -8255,11 +8255,11 @@
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>22153049.64</v>
+        <v>24522.29</v>
       </c>
     </row>
     <row r="129">
@@ -8316,11 +8316,11 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>792000</v>
+        <v>876.7</v>
       </c>
     </row>
     <row r="130">
@@ -8377,11 +8377,11 @@
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>25796106.16</v>
+        <v>28554.96</v>
       </c>
     </row>
     <row r="131">
@@ -8438,11 +8438,11 @@
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>23540000.17</v>
+        <v>26057.57</v>
       </c>
     </row>
     <row r="132">
@@ -8499,11 +8499,11 @@
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>23540000.17</v>
+        <v>26057.57</v>
       </c>
     </row>
     <row r="133">
@@ -8560,11 +8560,11 @@
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>204000.99</v>
+        <v>225.82</v>
       </c>
     </row>
     <row r="134">
@@ -8621,11 +8621,11 @@
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5549999.84</v>
+        <v>6143.56</v>
       </c>
     </row>
     <row r="135">
@@ -8682,11 +8682,11 @@
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3798574.96</v>
+        <v>4204.83</v>
       </c>
     </row>
     <row r="136">
@@ -8743,11 +8743,11 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>33941599.53</v>
+        <v>37571.61</v>
       </c>
     </row>
     <row r="137">
@@ -8804,11 +8804,11 @@
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>9499049.99</v>
+        <v>10514.96</v>
       </c>
     </row>
     <row r="138">
@@ -8865,11 +8865,11 @@
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>8000000.8</v>
+        <v>8855.59</v>
       </c>
     </row>
     <row r="139">
@@ -8926,11 +8926,11 @@
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>68399.77</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="140">
@@ -8987,11 +8987,11 @@
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>38999989</v>
+        <v>43170.98</v>
       </c>
     </row>
     <row r="141">
@@ -9048,11 +9048,11 @@
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>2804399.7</v>
+        <v>3104.33</v>
       </c>
     </row>
     <row r="142">
@@ -9109,11 +9109,11 @@
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>73760849.45</v>
+        <v>81649.47</v>
       </c>
     </row>
     <row r="143">
@@ -9170,11 +9170,11 @@
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>67164049.58</v>
+        <v>74347.14999999999</v>
       </c>
     </row>
     <row r="144">
@@ -9231,11 +9231,11 @@
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>9214049.810000001</v>
+        <v>10199.48</v>
       </c>
     </row>
     <row r="145">
@@ -9292,11 +9292,11 @@
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>28634900.27</v>
+        <v>31697.36</v>
       </c>
     </row>
     <row r="146">
@@ -9353,11 +9353,11 @@
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13530000.36</v>
+        <v>14977.02</v>
       </c>
     </row>
     <row r="147">
@@ -9414,11 +9414,11 @@
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>14999474</v>
+        <v>16603.65</v>
       </c>
     </row>
     <row r="148">
@@ -9479,11 +9479,11 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>659856237.6</v>
+        <v>730426.95</v>
       </c>
     </row>
     <row r="149">
@@ -9540,11 +9540,11 @@
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>291156.8</v>
+        <v>322.3</v>
       </c>
     </row>
     <row r="150">
@@ -9601,11 +9601,11 @@
       <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1500000.53</v>
+        <v>1660.42</v>
       </c>
     </row>
     <row r="151">
@@ -9662,11 +9662,11 @@
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2992000</v>
+        <v>3311.99</v>
       </c>
     </row>
     <row r="152">
@@ -9723,11 +9723,11 @@
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>249480</v>
+        <v>276.16</v>
       </c>
     </row>
     <row r="153">
@@ -9784,11 +9784,11 @@
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>70000000.40000001</v>
+        <v>77486.39999999999</v>
       </c>
     </row>
     <row r="154">
@@ -9845,11 +9845,11 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>19799999.81</v>
+        <v>21917.58</v>
       </c>
     </row>
     <row r="155">
@@ -9910,11 +9910,11 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>99749999.51000001</v>
+        <v>110418.12</v>
       </c>
     </row>
     <row r="156">
@@ -9971,11 +9971,11 @@
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>249480</v>
+        <v>276.16</v>
       </c>
     </row>
     <row r="157">
@@ -10032,11 +10032,11 @@
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>2112000</v>
+        <v>2337.88</v>
       </c>
     </row>
     <row r="158">
@@ -10093,11 +10093,11 @@
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>7913500</v>
+        <v>8759.84</v>
       </c>
     </row>
     <row r="159">
@@ -10154,11 +10154,11 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>285000.18</v>
+        <v>315.48</v>
       </c>
     </row>
     <row r="160">
@@ -10215,11 +10215,11 @@
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1685072.43</v>
+        <v>1865.29</v>
       </c>
     </row>
     <row r="161">
@@ -10276,11 +10276,11 @@
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>9262499.65</v>
+        <v>10253.11</v>
       </c>
     </row>
     <row r="162">
@@ -10337,11 +10337,11 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2069708.1</v>
+        <v>2291.06</v>
       </c>
     </row>
     <row r="163">
@@ -10398,11 +10398,11 @@
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>369600</v>
+        <v>409.13</v>
       </c>
     </row>
     <row r="164">
@@ -10459,11 +10459,11 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>382800</v>
+        <v>423.74</v>
       </c>
     </row>
     <row r="165">
@@ -10520,11 +10520,11 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>29194365.2</v>
+        <v>32316.66</v>
       </c>
     </row>
     <row r="166">
@@ -10581,11 +10581,11 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>13068000.05</v>
+        <v>14465.6</v>
       </c>
     </row>
     <row r="167">
@@ -10642,11 +10642,11 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>9000000.939999999</v>
+        <v>9962.540000000001</v>
       </c>
     </row>
     <row r="168">
@@ -10703,11 +10703,11 @@
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>700000.2</v>
+        <v>774.86</v>
       </c>
     </row>
     <row r="169">
@@ -10764,11 +10764,11 @@
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>17999999.62</v>
+        <v>19925.07</v>
       </c>
     </row>
     <row r="170">
@@ -10825,11 +10825,11 @@
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>35000000.77</v>
+        <v>38743.2</v>
       </c>
     </row>
     <row r="171">
@@ -10886,11 +10886,11 @@
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>37988599.61</v>
+        <v>42051.43</v>
       </c>
     </row>
     <row r="172">
@@ -10947,11 +10947,11 @@
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5077600</v>
+        <v>5620.64</v>
       </c>
     </row>
     <row r="173">
@@ -11008,11 +11008,11 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>23853550</v>
+        <v>26404.65</v>
       </c>
     </row>
     <row r="174">
@@ -11069,11 +11069,11 @@
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1799756</v>
+        <v>1992.24</v>
       </c>
     </row>
     <row r="175">
@@ -11130,11 +11130,11 @@
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>348462.4</v>
+        <v>385.73</v>
       </c>
     </row>
     <row r="176">
@@ -11191,11 +11191,11 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>949999.85</v>
+        <v>1051.6</v>
       </c>
     </row>
     <row r="177">
@@ -11252,11 +11252,11 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1045000.29</v>
+        <v>1156.76</v>
       </c>
     </row>
     <row r="178">
@@ -11313,11 +11313,11 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>55394500</v>
+        <v>61318.87</v>
       </c>
     </row>
     <row r="179">
@@ -11374,11 +11374,11 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>756000.4</v>
+        <v>836.85</v>
       </c>
     </row>
     <row r="180">
@@ -11435,11 +11435,11 @@
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>1120299.84</v>
+        <v>1240.11</v>
       </c>
     </row>
     <row r="181">
@@ -11496,11 +11496,11 @@
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>16018616.36</v>
+        <v>17731.79</v>
       </c>
     </row>
     <row r="182">
@@ -11557,11 +11557,11 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>8515801.01</v>
+        <v>9426.549999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11618,11 +11618,11 @@
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1999999.2</v>
+        <v>2213.9</v>
       </c>
     </row>
     <row r="184">
@@ -11679,11 +11679,11 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>218553.91</v>
+        <v>241.93</v>
       </c>
     </row>
     <row r="185">
@@ -11740,11 +11740,11 @@
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>371286920.21</v>
+        <v>410995.54</v>
       </c>
     </row>
     <row r="186">
@@ -11801,11 +11801,11 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3640000.86</v>
+        <v>4029.29</v>
       </c>
     </row>
     <row r="187">
@@ -11862,11 +11862,11 @@
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>2930400</v>
+        <v>3243.8</v>
       </c>
     </row>
     <row r="188">
@@ -11923,11 +11923,11 @@
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>54766800</v>
+        <v>60624.03</v>
       </c>
     </row>
     <row r="189">
@@ -11984,11 +11984,11 @@
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>144399.9</v>
+        <v>159.84</v>
       </c>
     </row>
     <row r="190">
@@ -12045,11 +12045,11 @@
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>880000</v>
+        <v>974.11</v>
       </c>
     </row>
     <row r="191">
@@ -12106,11 +12106,11 @@
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>500020.15</v>
+        <v>553.5</v>
       </c>
     </row>
     <row r="192">
@@ -12167,11 +12167,11 @@
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4640000.64</v>
+        <v>5136.24</v>
       </c>
     </row>
     <row r="193">
@@ -12228,11 +12228,11 @@
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>26998628.8</v>
+        <v>29886.09</v>
       </c>
     </row>
     <row r="194">
@@ -12289,11 +12289,11 @@
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>25057200.13</v>
+        <v>27737.03</v>
       </c>
     </row>
     <row r="195">
@@ -12350,11 +12350,11 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>32833235.86</v>
+        <v>36344.7</v>
       </c>
     </row>
     <row r="196">
@@ -12411,11 +12411,11 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>104500000.24</v>
+        <v>115676.13</v>
       </c>
     </row>
     <row r="197">
@@ -12472,11 +12472,11 @@
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>249999.2</v>
+        <v>276.74</v>
       </c>
     </row>
     <row r="198">
@@ -12533,11 +12533,11 @@
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2999998.32</v>
+        <v>3320.84</v>
       </c>
     </row>
     <row r="199">
@@ -12594,11 +12594,11 @@
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>455999.61</v>
+        <v>504.77</v>
       </c>
     </row>
     <row r="200">
@@ -12655,11 +12655,11 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>8093211.06</v>
+        <v>8958.77</v>
       </c>
     </row>
     <row r="201">
@@ -12716,11 +12716,11 @@
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>61064000.46</v>
+        <v>67594.71000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12777,11 +12777,11 @@
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>36684999.71</v>
+        <v>40608.41</v>
       </c>
     </row>
     <row r="203">
@@ -12838,11 +12838,11 @@
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>494999.6</v>
+        <v>547.9400000000001</v>
       </c>
     </row>
     <row r="204">
@@ -12899,11 +12899,11 @@
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>12847797.87</v>
+        <v>14221.85</v>
       </c>
     </row>
     <row r="205">
@@ -12960,11 +12960,11 @@
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2655584.07</v>
+        <v>2939.6</v>
       </c>
     </row>
     <row r="206">
@@ -13021,11 +13021,11 @@
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>12886616.98</v>
+        <v>14264.82</v>
       </c>
     </row>
     <row r="207">
@@ -13082,11 +13082,11 @@
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>599999.4</v>
+        <v>664.17</v>
       </c>
     </row>
     <row r="208">
@@ -13143,11 +13143,11 @@
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>4562280</v>
+        <v>5050.21</v>
       </c>
     </row>
     <row r="209">
@@ -13204,11 +13204,11 @@
       <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1337381.83</v>
+        <v>1480.41</v>
       </c>
     </row>
     <row r="210">
@@ -13265,11 +13265,11 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>37485417.33</v>
+        <v>41494.43</v>
       </c>
     </row>
     <row r="211">
@@ -13326,11 +13326,11 @@
       <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>17964281.25</v>
+        <v>19885.54</v>
       </c>
     </row>
     <row r="212">
@@ -13387,11 +13387,11 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>18000000.79</v>
+        <v>19925.08</v>
       </c>
     </row>
     <row r="213">
@@ -13448,11 +13448,11 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>16934399.53</v>
+        <v>18745.51</v>
       </c>
     </row>
     <row r="214">
@@ -13509,11 +13509,11 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>24449040.14</v>
+        <v>27063.83</v>
       </c>
     </row>
     <row r="215">
@@ -13570,11 +13570,11 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>38600240.39</v>
+        <v>42728.48</v>
       </c>
     </row>
     <row r="216">
@@ -13631,11 +13631,11 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>13213927.65</v>
+        <v>14627.14</v>
       </c>
     </row>
     <row r="217">
@@ -13692,11 +13692,11 @@
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>20000330</v>
+        <v>22139.34</v>
       </c>
     </row>
     <row r="218">
@@ -13753,11 +13753,11 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>49000000.32</v>
+        <v>54240.48</v>
       </c>
     </row>
     <row r="219">
@@ -13814,11 +13814,11 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>8152129.84</v>
+        <v>9023.99</v>
       </c>
     </row>
     <row r="220">
@@ -13875,11 +13875,11 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>19803349.49</v>
+        <v>21921.29</v>
       </c>
     </row>
     <row r="221">
@@ -13936,11 +13936,11 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1642200.86</v>
+        <v>1817.83</v>
       </c>
     </row>
     <row r="222">
@@ -13997,11 +13997,11 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>14700001.15</v>
+        <v>16272.15</v>
       </c>
     </row>
     <row r="223">
@@ -14058,11 +14058,11 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>12050519.53</v>
+        <v>13339.31</v>
       </c>
     </row>
     <row r="224">
@@ -14119,11 +14119,11 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>17890023.46</v>
+        <v>19803.34</v>
       </c>
     </row>
     <row r="225">
@@ -14180,11 +14180,11 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>50751260.71</v>
+        <v>56179.04</v>
       </c>
     </row>
     <row r="226">
@@ -14241,11 +14241,11 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>47744576.69</v>
+        <v>52850.79</v>
       </c>
     </row>
     <row r="227">
@@ -14302,11 +14302,11 @@
       <c r="K227" t="inlineStr"/>
       <c r="L227" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>35000000.23</v>
+        <v>38743.2</v>
       </c>
     </row>
     <row r="228">
@@ -14363,11 +14363,11 @@
       <c r="K228" t="inlineStr"/>
       <c r="L228" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>500000.09</v>
+        <v>553.47</v>
       </c>
     </row>
     <row r="229">
@@ -14424,11 +14424,11 @@
       <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>12000198</v>
+        <v>13283.6</v>
       </c>
     </row>
     <row r="230">
@@ -14485,11 +14485,11 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>22000193.9</v>
+        <v>24353.08</v>
       </c>
     </row>
     <row r="231">
@@ -14546,11 +14546,11 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>31100887.5</v>
+        <v>34427.08</v>
       </c>
     </row>
     <row r="232">
@@ -14607,11 +14607,11 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>10584000.87</v>
+        <v>11715.95</v>
       </c>
     </row>
     <row r="233">
@@ -14668,11 +14668,11 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>34911519.47</v>
+        <v>38645.26</v>
       </c>
     </row>
     <row r="234">
@@ -14729,11 +14729,11 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>571340.04</v>
+        <v>632.4400000000001</v>
       </c>
     </row>
     <row r="235">
@@ -14790,11 +14790,11 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>278809.8</v>
+        <v>308.63</v>
       </c>
     </row>
     <row r="236">
@@ -14851,11 +14851,11 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>10348800.49</v>
+        <v>11455.59</v>
       </c>
     </row>
     <row r="237">
@@ -14912,11 +14912,11 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>34807500.26</v>
+        <v>38530.11</v>
       </c>
     </row>
     <row r="238">
@@ -14973,11 +14973,11 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>6183775.5</v>
+        <v>6845.12</v>
       </c>
     </row>
     <row r="239">
@@ -15034,11 +15034,11 @@
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3728341.4</v>
+        <v>4127.08</v>
       </c>
     </row>
     <row r="240">
@@ -15095,11 +15095,11 @@
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>8857432.35</v>
+        <v>9804.719999999999</v>
       </c>
     </row>
     <row r="241">
@@ -15156,11 +15156,11 @@
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>16276330.36</v>
+        <v>18017.06</v>
       </c>
     </row>
     <row r="242">
@@ -15217,11 +15217,11 @@
       <c r="K242" t="inlineStr"/>
       <c r="L242" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>4965679.6</v>
+        <v>5496.75</v>
       </c>
     </row>
     <row r="243">
@@ -15278,11 +15278,11 @@
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>190000</v>
+        <v>210.32</v>
       </c>
     </row>
     <row r="244">
@@ -15339,11 +15339,11 @@
       <c r="K244" t="inlineStr"/>
       <c r="L244" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>15000000.27</v>
+        <v>16604.23</v>
       </c>
     </row>
     <row r="245">
@@ -15400,11 +15400,11 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>17000000.61</v>
+        <v>18818.13</v>
       </c>
     </row>
     <row r="246">
@@ -15461,11 +15461,11 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>5000000.87</v>
+        <v>5534.74</v>
       </c>
     </row>
     <row r="247">
@@ -15526,11 +15526,11 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>74065123.5999696</v>
+        <v>81986.28999999999</v>
       </c>
     </row>
     <row r="248">
@@ -15587,11 +15587,11 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>32422516.3</v>
+        <v>35890.06</v>
       </c>
     </row>
     <row r="249">
@@ -15648,11 +15648,11 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>8330028.99</v>
+        <v>9220.91</v>
       </c>
     </row>
     <row r="250">
@@ -15709,11 +15709,11 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>44244420.98</v>
+        <v>48976.3</v>
       </c>
     </row>
     <row r="251">
@@ -15770,11 +15770,11 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1600000.74</v>
+        <v>1771.12</v>
       </c>
     </row>
     <row r="252">
@@ -15831,11 +15831,11 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>18755338.03</v>
+        <v>20761.2</v>
       </c>
     </row>
     <row r="253">
@@ -15892,11 +15892,11 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>11362119.83</v>
+        <v>12577.28</v>
       </c>
     </row>
     <row r="254">
@@ -15953,11 +15953,11 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>19000000.96</v>
+        <v>21032.02</v>
       </c>
     </row>
     <row r="255">
@@ -16014,11 +16014,11 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>22000000.31</v>
+        <v>24352.87</v>
       </c>
     </row>
     <row r="256">
@@ -16075,11 +16075,11 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>101136.36</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="257">
@@ -16136,11 +16136,11 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>29155000</v>
+        <v>32273.09</v>
       </c>
     </row>
     <row r="258">
@@ -16197,11 +16197,11 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>10477180.45</v>
+        <v>11597.7</v>
       </c>
     </row>
     <row r="259">
@@ -16258,11 +16258,11 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>58757553.74</v>
+        <v>65041.59</v>
       </c>
     </row>
     <row r="260">
@@ -16319,11 +16319,11 @@
       <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>15531090.08</v>
+        <v>17192.12</v>
       </c>
     </row>
     <row r="261">
@@ -16380,11 +16380,11 @@
       <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>5000665.6</v>
+        <v>5535.48</v>
       </c>
     </row>
     <row r="262">
@@ -16441,11 +16441,11 @@
       <c r="K262" t="inlineStr"/>
       <c r="L262" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>12011860</v>
+        <v>13296.51</v>
       </c>
     </row>
     <row r="263">
@@ -16502,11 +16502,11 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>26959799.93</v>
+        <v>29843.11</v>
       </c>
     </row>
     <row r="264">
@@ -16563,11 +16563,11 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>30000000.53</v>
+        <v>33208.46</v>
       </c>
     </row>
   </sheetData>
